--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260608.xlsx
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
